--- a/Sex_Pheromone_Study/Data/GC-EAD data.xlsx
+++ b/Sex_Pheromone_Study/Data/GC-EAD data.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Esmael/Desktop/Data Science Library/Data for play/Fall-Armyworm-Study/Sex_Pheromone_Study/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC85DF34-ED18-D244-9D10-ACD5FDBAF2CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3585C8F4-CB13-C64D-9055-C732B4641DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="35840" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$147</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="18">
   <si>
     <t>wavename</t>
   </si>
@@ -443,7 +443,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S145"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:S147"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="9.83203125" bestFit="1" customWidth="1"/>
@@ -495,7 +496,7 @@
       <c r="R1" s="2"/>
       <c r="S1" s="2"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -529,7 +530,7 @@
       <c r="R2" s="2"/>
       <c r="S2" s="2"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
@@ -563,7 +564,7 @@
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
@@ -597,7 +598,7 @@
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
@@ -631,7 +632,7 @@
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -665,7 +666,7 @@
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -699,7 +700,7 @@
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
@@ -728,7 +729,7 @@
         <v>20220906</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -757,7 +758,7 @@
         <v>20220906</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
@@ -791,7 +792,7 @@
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -825,7 +826,7 @@
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
@@ -859,7 +860,7 @@
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
@@ -893,7 +894,7 @@
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -927,7 +928,7 @@
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>17</v>
       </c>
@@ -961,7 +962,7 @@
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
@@ -995,7 +996,7 @@
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>17</v>
       </c>
@@ -1029,7 +1030,7 @@
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -1063,7 +1064,7 @@
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
@@ -1097,7 +1098,7 @@
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>17</v>
       </c>
@@ -1131,7 +1132,7 @@
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>17</v>
       </c>
@@ -1165,7 +1166,7 @@
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1233,7 +1234,7 @@
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>16</v>
       </c>
@@ -1301,7 +1302,7 @@
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>16</v>
       </c>
@@ -1505,7 +1506,7 @@
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>16</v>
       </c>
@@ -1539,7 +1540,7 @@
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>16</v>
       </c>
@@ -1607,7 +1608,7 @@
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>16</v>
       </c>
@@ -1709,7 +1710,7 @@
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>16</v>
       </c>
@@ -1777,7 +1778,7 @@
       <c r="O39" s="2"/>
       <c r="P39" s="2"/>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>16</v>
       </c>
@@ -1913,7 +1914,7 @@
       <c r="O43" s="2"/>
       <c r="P43" s="2"/>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>17</v>
       </c>
@@ -1947,7 +1948,7 @@
       <c r="O44" s="2"/>
       <c r="P44" s="2"/>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>17</v>
       </c>
@@ -1981,7 +1982,7 @@
       <c r="O45" s="2"/>
       <c r="P45" s="2"/>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>17</v>
       </c>
@@ -2015,7 +2016,7 @@
       <c r="O46" s="3"/>
       <c r="P46" s="3"/>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>17</v>
       </c>
@@ -2050,7 +2051,7 @@
       <c r="P47" s="3"/>
       <c r="Q47" s="3"/>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>17</v>
       </c>
@@ -2085,7 +2086,7 @@
       <c r="P48" s="3"/>
       <c r="Q48" s="3"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>17</v>
       </c>
@@ -2120,7 +2121,7 @@
       <c r="P49" s="3"/>
       <c r="Q49" s="3"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>17</v>
       </c>
@@ -2155,7 +2156,7 @@
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>17</v>
       </c>
@@ -2190,7 +2191,7 @@
       <c r="P51" s="3"/>
       <c r="Q51" s="3"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>17</v>
       </c>
@@ -2225,7 +2226,7 @@
       <c r="P52" s="3"/>
       <c r="Q52" s="3"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>17</v>
       </c>
@@ -2260,7 +2261,7 @@
       <c r="P53" s="3"/>
       <c r="Q53" s="3"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>17</v>
       </c>
@@ -2294,7 +2295,7 @@
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>17</v>
       </c>
@@ -2328,7 +2329,7 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>17</v>
       </c>
@@ -2362,7 +2363,7 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>17</v>
       </c>
@@ -2396,7 +2397,7 @@
       <c r="O57" s="3"/>
       <c r="P57" s="3"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>17</v>
       </c>
@@ -2430,7 +2431,7 @@
       <c r="O58" s="3"/>
       <c r="P58" s="3"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>17</v>
       </c>
@@ -2464,7 +2465,7 @@
       <c r="O59" s="3"/>
       <c r="P59" s="3"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>17</v>
       </c>
@@ -2498,7 +2499,7 @@
       <c r="O60" s="3"/>
       <c r="P60" s="3"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>17</v>
       </c>
@@ -2532,7 +2533,7 @@
       <c r="O61" s="3"/>
       <c r="P61" s="3"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>17</v>
       </c>
@@ -2566,7 +2567,7 @@
       <c r="O62" s="3"/>
       <c r="P62" s="3"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>17</v>
       </c>
@@ -2600,7 +2601,7 @@
       <c r="O63" s="3"/>
       <c r="P63" s="3"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>17</v>
       </c>
@@ -2634,7 +2635,7 @@
       <c r="O64" s="3"/>
       <c r="P64" s="3"/>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>17</v>
       </c>
@@ -2668,7 +2669,7 @@
       <c r="O65" s="3"/>
       <c r="P65" s="3"/>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>17</v>
       </c>
@@ -2702,7 +2703,7 @@
       <c r="O66" s="3"/>
       <c r="P66" s="3"/>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>17</v>
       </c>
@@ -2736,7 +2737,7 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>17</v>
       </c>
@@ -2770,7 +2771,7 @@
       <c r="O68" s="3"/>
       <c r="P68" s="3"/>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>17</v>
       </c>
@@ -2804,7 +2805,7 @@
       <c r="O69" s="3"/>
       <c r="P69" s="3"/>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>16</v>
       </c>
@@ -2838,7 +2839,7 @@
       <c r="O70" s="3"/>
       <c r="P70" s="3"/>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>16</v>
       </c>
@@ -2906,7 +2907,7 @@
       <c r="O72" s="3"/>
       <c r="P72" s="3"/>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>16</v>
       </c>
@@ -3111,7 +3112,7 @@
       <c r="O78" s="3"/>
       <c r="P78" s="3"/>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>16</v>
       </c>
@@ -3272,7 +3273,7 @@
         <v>20220819</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>16</v>
       </c>
@@ -3359,7 +3360,7 @@
         <v>20221121</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>16</v>
       </c>
@@ -3684,7 +3685,7 @@
       <c r="N96" s="3"/>
       <c r="O96" s="3"/>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>16</v>
       </c>
@@ -3922,7 +3923,7 @@
       <c r="N103" s="3"/>
       <c r="O103" s="3"/>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
         <v>16</v>
       </c>
@@ -3956,7 +3957,7 @@
       <c r="N104" s="3"/>
       <c r="O104" s="3"/>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
         <v>16</v>
       </c>
@@ -3990,7 +3991,7 @@
       <c r="N105" s="3"/>
       <c r="O105" s="3"/>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
         <v>16</v>
       </c>
@@ -4058,7 +4059,7 @@
       <c r="N107" s="3"/>
       <c r="O107" s="3"/>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
         <v>16</v>
       </c>
@@ -4162,7 +4163,7 @@
       <c r="O110" s="3"/>
       <c r="P110" s="3"/>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
         <v>16</v>
       </c>
@@ -4197,7 +4198,7 @@
       <c r="O111" s="3"/>
       <c r="P111" s="3"/>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
         <v>16</v>
       </c>
@@ -4232,7 +4233,7 @@
       <c r="O112" s="3"/>
       <c r="P112" s="3"/>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
         <v>16</v>
       </c>
@@ -4302,7 +4303,7 @@
       <c r="O114" s="3"/>
       <c r="P114" s="3"/>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
         <v>16</v>
       </c>
@@ -4337,7 +4338,7 @@
       <c r="O115" s="3"/>
       <c r="P115" s="3"/>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
         <v>16</v>
       </c>
@@ -4396,7 +4397,7 @@
       </c>
       <c r="K117" s="6"/>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
         <v>16</v>
       </c>
@@ -4454,7 +4455,7 @@
         <v>20220729</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>17</v>
       </c>
@@ -4483,7 +4484,7 @@
         <v>20230126</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
         <v>17</v>
       </c>
@@ -4512,7 +4513,7 @@
         <v>20230126</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
         <v>17</v>
       </c>
@@ -4541,7 +4542,7 @@
         <v>20230126</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
         <v>17</v>
       </c>
@@ -4570,7 +4571,7 @@
         <v>20230126</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
         <v>17</v>
       </c>
@@ -4600,7 +4601,7 @@
       </c>
       <c r="K124" s="6"/>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
         <v>17</v>
       </c>
@@ -4629,7 +4630,7 @@
         <v>20230126</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
         <v>17</v>
       </c>
@@ -4658,7 +4659,7 @@
         <v>20230126</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
         <v>17</v>
       </c>
@@ -4687,7 +4688,7 @@
         <v>20230126</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
         <v>17</v>
       </c>
@@ -4716,7 +4717,7 @@
         <v>20230126</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
         <v>17</v>
       </c>
@@ -4745,7 +4746,7 @@
         <v>20230126</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
         <v>17</v>
       </c>
@@ -4774,7 +4775,7 @@
         <v>20230126</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
         <v>17</v>
       </c>
@@ -4803,7 +4804,7 @@
         <v>20230126</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
         <v>17</v>
       </c>
@@ -4832,7 +4833,7 @@
         <v>20230126</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
         <v>17</v>
       </c>
@@ -4862,7 +4863,7 @@
       </c>
       <c r="K133" s="6"/>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
         <v>17</v>
       </c>
@@ -4998,7 +4999,7 @@
       <c r="N137" s="3"/>
       <c r="O137" s="3"/>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
         <v>16</v>
       </c>
@@ -5135,6 +5136,33 @@
       <c r="O141" s="3"/>
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A142" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B142" s="1">
+        <v>0</v>
+      </c>
+      <c r="C142" s="1">
+        <v>5</v>
+      </c>
+      <c r="D142" s="1">
+        <v>213</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F142" s="1">
+        <v>17.975999999999999</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H142" s="2">
+        <v>6.0057300000000001E-2</v>
+      </c>
+      <c r="I142" s="1">
+        <v>20220125</v>
+      </c>
       <c r="K142" s="3"/>
       <c r="L142" s="3"/>
       <c r="M142" s="3"/>
@@ -5142,6 +5170,33 @@
       <c r="O142" s="3"/>
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A143" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B143" s="1">
+        <v>0</v>
+      </c>
+      <c r="C143" s="1">
+        <v>6</v>
+      </c>
+      <c r="D143" s="1">
+        <v>213</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F143" s="1">
+        <v>17.975999999999999</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H143" s="2">
+        <v>7.0023100000000005E-2</v>
+      </c>
+      <c r="I143" s="1">
+        <v>20220125</v>
+      </c>
       <c r="K143" s="3"/>
       <c r="L143" s="3"/>
       <c r="M143" s="3"/>
@@ -5149,21 +5204,144 @@
       <c r="O143" s="3"/>
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A144" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B144" s="1">
+        <v>0</v>
+      </c>
+      <c r="C144" s="1">
+        <v>7</v>
+      </c>
+      <c r="D144" s="1">
+        <v>213</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F144" s="1">
+        <v>17.975999999999999</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H144" s="2">
+        <v>6.0057300000000001E-2</v>
+      </c>
+      <c r="I144" s="1">
+        <v>20220125</v>
+      </c>
       <c r="K144" s="3"/>
       <c r="L144" s="3"/>
       <c r="M144" s="3"/>
       <c r="N144" s="3"/>
       <c r="O144" s="3"/>
     </row>
-    <row r="145" spans="11:15" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A145" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B145" s="1">
+        <v>0</v>
+      </c>
+      <c r="C145" s="1">
+        <v>12</v>
+      </c>
+      <c r="D145" s="1">
+        <v>203</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F145" s="3">
+        <v>17.952200000000001</v>
+      </c>
+      <c r="G145" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H145" s="2">
+        <v>7.0023100000000005E-2</v>
+      </c>
+      <c r="I145" s="1">
+        <v>20230126</v>
+      </c>
       <c r="K145" s="3"/>
       <c r="L145" s="3"/>
       <c r="M145" s="3"/>
       <c r="N145" s="3"/>
       <c r="O145" s="3"/>
     </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A146" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B146" s="1">
+        <v>0</v>
+      </c>
+      <c r="C146" s="1">
+        <v>13</v>
+      </c>
+      <c r="D146" s="1">
+        <v>203</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F146" s="3">
+        <v>17.938700000000001</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H146" s="2">
+        <v>6.0057300000000001E-2</v>
+      </c>
+      <c r="I146" s="1">
+        <v>20230126</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A147" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B147" s="1">
+        <v>0</v>
+      </c>
+      <c r="C147" s="1">
+        <v>14</v>
+      </c>
+      <c r="D147" s="1">
+        <v>203</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F147" s="3">
+        <v>17.9528</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H147" s="2">
+        <v>0.56779100000000005</v>
+      </c>
+      <c r="I147" s="1">
+        <v>20230126</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I141" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I147" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="FAW"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="6">
+      <filters>
+        <filter val="Z-9-14"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I146">
     <sortCondition ref="E1:E146"/>
   </sortState>
